--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47133-2024 artfynd.xlsx
+++ b/artfynd/A 47133-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000356</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
